--- a/Calibration/Calibration Constant.xlsx
+++ b/Calibration/Calibration Constant.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Thesis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Thesis\Calibration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A603A31-05D1-4957-A1A1-67991ED99ACC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F17FD30F-9789-4D0C-A766-2839AD349494}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{7FD7F354-8DEB-4761-9516-CD2B7AB37711}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="75">
   <si>
     <t xml:space="preserve">Calibration Constant Determination </t>
   </si>
@@ -278,11 +278,20 @@
   <si>
     <t>w/c ratio</t>
   </si>
+  <si>
+    <t>Time(s)</t>
+  </si>
+  <si>
+    <t>T(t) in Kelvin</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="0.0"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -467,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -486,9 +495,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -522,6 +528,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -537,6 +555,1239 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Calibration Cooling Curve</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Temperature Values</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:name>Cooling Curve</c:name>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="exp"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.22400612423447069"/>
+                  <c:y val="-4.5756415864683583E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1"/>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>T_t = T_amb + (T_initial - T_amb)e</a:t>
+                    </a:r>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="30000"/>
+                      <a:t>(-k/c)t</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US" baseline="0"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1"/>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Calibration '!$G$36:$G$56</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>600</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2200</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2600</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2800</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3200</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3400</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3600</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3800</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Calibration '!$I$36:$I$56</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="21"/>
+                <c:pt idx="0">
+                  <c:v>59.9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>59.815018960544634</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>59.730234165031305</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>59.645645160280274</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>59.561251494158327</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>59.477052715576342</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>59.393048374486874</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>59.309238021881775</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>59.22562120978975</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>59.142197491274025</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>59.058966420429897</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>58.97592755238238</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>58.893080443283822</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>58.810424650311546</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>58.727959731665457</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>58.645685246565705</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>58.563600755250313</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>58.481705818972834</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>58.4</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>58.31848286160939</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>58.237153968087092</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BAA9-4ED2-9BE9-7213EC39FD15}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="t"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="450169264"/>
+        <c:axId val="450161104"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="450169264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Time</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="en-US" baseline="0"/>
+                  <a:t>, Seconds</a:t>
+                </a:r>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450161104"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="450161104"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1"/>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Temperature, Celsius</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:overlay val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln cap="sq">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1"/>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+        </c:title>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="450169264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:round/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:legendEntry>
+        <c:idx val="1"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:legendEntry>
+        <c:idx val="3"/>
+        <c:delete val="1"/>
+      </c:legendEntry>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.61062401574803149"/>
+          <c:y val="0.22763815981335667"/>
+          <c:w val="0.30387598425196849"/>
+          <c:h val="0.15625109361329836"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:defRPr>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -583,6 +1834,42 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>426720</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>102870</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>563880</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>102870</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64058DF2-8EC2-CC61-6B81-B1749A7D80ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -905,14 +2192,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BFE3CA3-1DFB-438C-85F9-ABC945CA0207}">
-  <dimension ref="A1:T30"/>
+  <dimension ref="A1:T56"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="5" max="5" width="2.88671875" customWidth="1"/>
     <col min="6" max="6" width="3" customWidth="1"/>
     <col min="7" max="7" width="23.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.6640625" style="3" customWidth="1"/>
-    <col min="9" max="9" width="8.88671875" style="1"/>
+    <col min="8" max="8" width="7.88671875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="12.88671875" style="1" customWidth="1"/>
     <col min="15" max="15" width="20.21875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -931,35 +2218,35 @@
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="11"/>
-      <c r="M2" s="12"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
+      <c r="M2" s="11"/>
     </row>
     <row r="3" spans="1:20" ht="14.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="H3" s="13"/>
-      <c r="I3" s="14"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="14"/>
-      <c r="M3" s="15"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="14"/>
     </row>
     <row r="4" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="5" spans="1:20" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G5" s="16" t="s">
+      <c r="G5" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H5" s="17"/>
-      <c r="I5" s="18"/>
-      <c r="L5" s="9" t="s">
+      <c r="H5" s="16"/>
+      <c r="I5" s="17"/>
+      <c r="L5" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
+      <c r="M5" s="8"/>
+      <c r="N5" s="8"/>
       <c r="O5" s="6">
         <f>(H11*H19)/(H17-H16)</f>
         <v>3076.9230769230771</v>
@@ -988,11 +2275,11 @@
       <c r="I6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L6" s="19" t="s">
+      <c r="L6" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="M6" s="19"/>
-      <c r="N6" s="19"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
       <c r="O6" s="1" t="s">
         <v>30</v>
       </c>
@@ -1019,11 +2306,11 @@
       <c r="I7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="M7" s="19"/>
-      <c r="N7" s="19"/>
+      <c r="M7" s="18"/>
+      <c r="N7" s="18"/>
       <c r="O7" s="1" t="s">
         <v>29</v>
       </c>
@@ -1041,11 +2328,11 @@
       <c r="I8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
+      <c r="M8" s="8"/>
+      <c r="N8" s="8"/>
       <c r="O8" s="1" t="s">
         <v>35</v>
       </c>
@@ -1182,11 +2469,11 @@
     </row>
     <row r="20" spans="7:18" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="21" spans="7:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G21" s="16" t="s">
+      <c r="G21" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="18"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="17"/>
     </row>
     <row r="22" spans="7:18" x14ac:dyDescent="0.3">
       <c r="G22" t="s">
@@ -1245,10 +2532,10 @@
       <c r="N27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="O27" s="9" t="s">
+      <c r="O27" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="P27" s="9"/>
+      <c r="P27" s="8"/>
     </row>
     <row r="28" spans="7:18" x14ac:dyDescent="0.3">
       <c r="G28" t="s">
@@ -1303,8 +2590,228 @@
         <v>24</v>
       </c>
     </row>
+    <row r="35" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G35" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" s="20"/>
+      <c r="I35" s="21" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G36">
+        <v>0</v>
+      </c>
+      <c r="H36"/>
+      <c r="I36" s="22">
+        <f>$H$29 + ($H$27-$H$29)*EXP((-$O$28/$O$5)*G36)</f>
+        <v>59.9</v>
+      </c>
+    </row>
+    <row r="37" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G37">
+        <v>200</v>
+      </c>
+      <c r="H37"/>
+      <c r="I37" s="22">
+        <f>$H$29 + ($H$27-$H$29)*EXP((-$O$28/$O$5)*G37)</f>
+        <v>59.815018960544634</v>
+      </c>
+    </row>
+    <row r="38" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G38">
+        <v>400</v>
+      </c>
+      <c r="H38"/>
+      <c r="I38" s="22">
+        <f t="shared" ref="I38:I56" si="1">$H$29 + ($H$27-$H$29)*EXP((-$O$28/$O$5)*G38)</f>
+        <v>59.730234165031305</v>
+      </c>
+    </row>
+    <row r="39" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G39">
+        <v>600</v>
+      </c>
+      <c r="H39"/>
+      <c r="I39" s="22">
+        <f t="shared" si="1"/>
+        <v>59.645645160280274</v>
+      </c>
+    </row>
+    <row r="40" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G40">
+        <v>800</v>
+      </c>
+      <c r="H40"/>
+      <c r="I40" s="22">
+        <f t="shared" si="1"/>
+        <v>59.561251494158327</v>
+      </c>
+    </row>
+    <row r="41" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G41">
+        <v>1000</v>
+      </c>
+      <c r="H41"/>
+      <c r="I41" s="22">
+        <f t="shared" si="1"/>
+        <v>59.477052715576342</v>
+      </c>
+    </row>
+    <row r="42" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G42">
+        <v>1200</v>
+      </c>
+      <c r="H42"/>
+      <c r="I42" s="22">
+        <f t="shared" si="1"/>
+        <v>59.393048374486874</v>
+      </c>
+    </row>
+    <row r="43" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G43">
+        <v>1400</v>
+      </c>
+      <c r="H43"/>
+      <c r="I43" s="22">
+        <f t="shared" si="1"/>
+        <v>59.309238021881775</v>
+      </c>
+    </row>
+    <row r="44" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G44">
+        <v>1600</v>
+      </c>
+      <c r="H44"/>
+      <c r="I44" s="22">
+        <f t="shared" si="1"/>
+        <v>59.22562120978975</v>
+      </c>
+    </row>
+    <row r="45" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G45">
+        <v>1800</v>
+      </c>
+      <c r="H45"/>
+      <c r="I45" s="22">
+        <f t="shared" si="1"/>
+        <v>59.142197491274025</v>
+      </c>
+    </row>
+    <row r="46" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G46">
+        <v>2000</v>
+      </c>
+      <c r="H46"/>
+      <c r="I46" s="22">
+        <f t="shared" si="1"/>
+        <v>59.058966420429897</v>
+      </c>
+    </row>
+    <row r="47" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G47">
+        <v>2200</v>
+      </c>
+      <c r="H47"/>
+      <c r="I47" s="22">
+        <f t="shared" si="1"/>
+        <v>58.97592755238238</v>
+      </c>
+    </row>
+    <row r="48" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G48">
+        <v>2400</v>
+      </c>
+      <c r="H48"/>
+      <c r="I48" s="22">
+        <f t="shared" si="1"/>
+        <v>58.893080443283822</v>
+      </c>
+    </row>
+    <row r="49" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G49">
+        <v>2600</v>
+      </c>
+      <c r="H49"/>
+      <c r="I49" s="22">
+        <f t="shared" si="1"/>
+        <v>58.810424650311546</v>
+      </c>
+    </row>
+    <row r="50" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G50">
+        <v>2800</v>
+      </c>
+      <c r="H50"/>
+      <c r="I50" s="22">
+        <f t="shared" si="1"/>
+        <v>58.727959731665457</v>
+      </c>
+    </row>
+    <row r="51" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G51">
+        <v>3000</v>
+      </c>
+      <c r="H51"/>
+      <c r="I51" s="22">
+        <f t="shared" si="1"/>
+        <v>58.645685246565705</v>
+      </c>
+    </row>
+    <row r="52" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G52">
+        <v>3200</v>
+      </c>
+      <c r="H52"/>
+      <c r="I52" s="22">
+        <f t="shared" si="1"/>
+        <v>58.563600755250313</v>
+      </c>
+    </row>
+    <row r="53" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G53">
+        <v>3400</v>
+      </c>
+      <c r="H53"/>
+      <c r="I53" s="22">
+        <f t="shared" si="1"/>
+        <v>58.481705818972834</v>
+      </c>
+    </row>
+    <row r="54" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G54">
+        <v>3600</v>
+      </c>
+      <c r="H54"/>
+      <c r="I54" s="22">
+        <f t="shared" si="1"/>
+        <v>58.4</v>
+      </c>
+    </row>
+    <row r="55" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G55">
+        <v>3800</v>
+      </c>
+      <c r="H55"/>
+      <c r="I55" s="22">
+        <f t="shared" si="1"/>
+        <v>58.31848286160939</v>
+      </c>
+    </row>
+    <row r="56" spans="7:9" x14ac:dyDescent="0.3">
+      <c r="G56">
+        <v>4000</v>
+      </c>
+      <c r="H56"/>
+      <c r="I56" s="22">
+        <f t="shared" si="1"/>
+        <v>58.237153968087092</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="G35:H35"/>
     <mergeCell ref="O27:P27"/>
     <mergeCell ref="H2:M3"/>
     <mergeCell ref="G5:I5"/>
@@ -2812,21 +4319,21 @@
       </c>
     </row>
     <row r="49" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F49" s="8" t="s">
+      <c r="F49" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="G49" s="8"/>
-      <c r="H49" s="8"/>
+      <c r="G49" s="19"/>
+      <c r="H49" s="19"/>
     </row>
     <row r="50" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
+      <c r="H50" s="19"/>
     </row>
     <row r="51" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
+      <c r="F51" s="19"/>
+      <c r="G51" s="19"/>
+      <c r="H51" s="19"/>
     </row>
     <row r="54" spans="6:11" x14ac:dyDescent="0.3">
       <c r="F54">
@@ -3197,21 +4704,21 @@
       </c>
     </row>
     <row r="77" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F77" s="8" t="s">
+      <c r="F77" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="G77" s="8"/>
-      <c r="H77" s="8"/>
+      <c r="G77" s="19"/>
+      <c r="H77" s="19"/>
     </row>
     <row r="78" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F78" s="8"/>
-      <c r="G78" s="8"/>
-      <c r="H78" s="8"/>
+      <c r="F78" s="19"/>
+      <c r="G78" s="19"/>
+      <c r="H78" s="19"/>
     </row>
     <row r="79" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F79" s="8"/>
-      <c r="G79" s="8"/>
-      <c r="H79" s="8"/>
+      <c r="F79" s="19"/>
+      <c r="G79" s="19"/>
+      <c r="H79" s="19"/>
     </row>
     <row r="82" spans="6:11" x14ac:dyDescent="0.3">
       <c r="F82">
@@ -3292,21 +4799,21 @@
       </c>
     </row>
     <row r="88" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F88" s="8" t="s">
+      <c r="F88" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="G88" s="8"/>
-      <c r="H88" s="8"/>
+      <c r="G88" s="19"/>
+      <c r="H88" s="19"/>
     </row>
     <row r="89" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F89" s="8"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="8"/>
+      <c r="F89" s="19"/>
+      <c r="G89" s="19"/>
+      <c r="H89" s="19"/>
     </row>
     <row r="90" spans="6:11" x14ac:dyDescent="0.3">
-      <c r="F90" s="8"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="8"/>
+      <c r="F90" s="19"/>
+      <c r="G90" s="19"/>
+      <c r="H90" s="19"/>
     </row>
     <row r="93" spans="6:11" x14ac:dyDescent="0.3">
       <c r="F93">
